--- a/config/citysound.xlsx
+++ b/config/citysound.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="15135" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="citysound" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="citysound" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>エリシアムレコード</t>
+          <t>伊利亚姆唱片</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>踊る、宇宙の中で</t>
+          <t>跳舞，在宇宙中</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
